--- a/backend/data/attachments/wealth_投资者教育活动方案_6.xlsx
+++ b/backend/data/attachments/wealth_投资者教育活动方案_6.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="D2" t="n">
-        <v>12046</v>
+        <v>7902</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>216</v>
+        <v>352</v>
       </c>
       <c r="C3" t="n">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="D3" t="n">
-        <v>2388</v>
+        <v>4090</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1316</v>
+        <v>1894</v>
       </c>
       <c r="C4" t="n">
-        <v>625</v>
+        <v>778</v>
       </c>
       <c r="D4" t="n">
-        <v>397</v>
+        <v>958</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -564,14 +564,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
